--- a/StructureDefinition-ct-anterior-chamber.xlsx
+++ b/StructureDefinition-ct-anterior-chamber.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ct-anterior-chamber.xlsx
+++ b/StructureDefinition-ct-anterior-chamber.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ct-anterior-chamber.xlsx
+++ b/StructureDefinition-ct-anterior-chamber.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -759,7 +759,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
 </t>
   </si>
   <si>
@@ -4295,7 +4295,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>233</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4417,7 +4417,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
